--- a/lib/plantillas-aseguradoras/previsora.xlsx
+++ b/lib/plantillas-aseguradoras/previsora.xlsx
@@ -439,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP54"/>
+  <dimension ref="A1:AP61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -573,10 +573,2016 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="W3">
+        <f>+T3*S3</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f>U3-W3</f>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f>+F3-E3</f>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f>+X3*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f>+(X3*(V3/1000)+(Z3*(V3/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f>+(AA3/365)*Y3</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f>+AB3*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f>+AB3+AC3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="W4">
+        <f>+T4*S4</f>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f>U4-W4</f>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f>+F4-E4</f>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f>+X4*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f>+(X4*(V4/1000)+(Z4*(V4/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f>+(AA4/365)*Y4</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f>+AB4*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f>+AB4+AC4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="W5">
+        <f>+T5*S5</f>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f>U5-W5</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <f>+F5-E5</f>
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <f>+X5*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f>+(X5*(V5/1000)+(Z5*(V5/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f>+(AA5/365)*Y5</f>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f>+AB5*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>+AB5+AC5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="W6">
+        <f>+T6*S6</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f>U6-W6</f>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f>+F6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f>+X6*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f>+(X6*(V6/1000)+(Z6*(V6/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f>+(AA6/365)*Y6</f>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f>+AB6*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f>+AB6+AC6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="W7">
+        <f>+T7*S7</f>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f>U7-W7</f>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f>+F7-E7</f>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f>+X7*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f>+(X7*(V7/1000)+(Z7*(V7/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f>+(AA7/365)*Y7</f>
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <f>+AB7*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <f>+AB7+AC7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="W8">
+        <f>+T8*S8</f>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f>U8-W8</f>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f>+F8-E8</f>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f>+X8*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f>+(X8*(V8/1000)+(Z8*(V8/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f>+(AA8/365)*Y8</f>
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <f>+AB8*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <f>+AB8+AC8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="W9">
+        <f>+T9*S9</f>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f>U9-W9</f>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f>+F9-E9</f>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f>+X9*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f>+(X9*(V9/1000)+(Z9*(V9/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f>+(AA9/365)*Y9</f>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f>+AB9*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f>+AB9+AC9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="W10">
+        <f>+T10*S10</f>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f>U10-W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f>+F10-E10</f>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f>+X10*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f>+(X10*(V10/1000)+(Z10*(V10/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f>+(AA10/365)*Y10</f>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f>+AB10*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f>+AB10+AC10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="W11">
+        <f>+T11*S11</f>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f>U11-W11</f>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f>+F11-E11</f>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f>+X11*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f>+(X11*(V11/1000)+(Z11*(V11/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f>+(AA11/365)*Y11</f>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f>+AB11*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f>+AB11+AC11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="W12">
+        <f>+T12*S12</f>
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <f>U12-W12</f>
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <f>+F12-E12</f>
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <f>+X12*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f>+(X12*(V12/1000)+(Z12*(V12/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <f>+(AA12/365)*Y12</f>
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <f>+AB12*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <f>+AB12+AC12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="W13">
+        <f>+T13*S13</f>
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <f>U13-W13</f>
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <f>+F13-E13</f>
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <f>+X13*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <f>+(X13*(V13/1000)+(Z13*(V13/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <f>+(AA13/365)*Y13</f>
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <f>+AB13*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <f>+AB13+AC13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="W14">
+        <f>+T14*S14</f>
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <f>U14-W14</f>
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <f>+F14-E14</f>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f>+X14*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f>+(X14*(V14/1000)+(Z14*(V14/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f>+(AA14/365)*Y14</f>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f>+AB14*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f>+AB14+AC14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="W15">
+        <f>+T15*S15</f>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f>U15-W15</f>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f>+F15-E15</f>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f>+X15*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f>+(X15*(V15/1000)+(Z15*(V15/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f>+(AA15/365)*Y15</f>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f>+AB15*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f>+AB15+AC15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="W16">
+        <f>+T16*S16</f>
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <f>U16-W16</f>
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <f>+F16-E16</f>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f>+X16*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <f>+(X16*(V16/1000)+(Z16*(V16/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <f>+(AA16/365)*Y16</f>
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <f>+AB16*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <f>+AB16+AC16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="W17">
+        <f>+T17*S17</f>
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <f>U17-W17</f>
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <f>+F17-E17</f>
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <f>+X17*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <f>+(X17*(V17/1000)+(Z17*(V17/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <f>+(AA17/365)*Y17</f>
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <f>+AB17*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <f>+AB17+AC17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="W18">
+        <f>+T18*S18</f>
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <f>U18-W18</f>
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <f>+F18-E18</f>
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <f>+X18*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f>+(X18*(V18/1000)+(Z18*(V18/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f>+(AA18/365)*Y18</f>
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <f>+AB18*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <f>+AB18+AC18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="W19">
+        <f>+T19*S19</f>
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <f>U19-W19</f>
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <f>+F19-E19</f>
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <f>+X19*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <f>+(X19*(V19/1000)+(Z19*(V19/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <f>+(AA19/365)*Y19</f>
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <f>+AB19*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <f>+AB19+AC19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="W20">
+        <f>+T20*S20</f>
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <f>U20-W20</f>
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <f>+F20-E20</f>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f>+X20*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <f>+(X20*(V20/1000)+(Z20*(V20/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <f>+(AA20/365)*Y20</f>
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <f>+AB20*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <f>+AB20+AC20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="W21">
+        <f>+T21*S21</f>
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <f>U21-W21</f>
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <f>+F21-E21</f>
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <f>+X21*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f>+(X21*(V21/1000)+(Z21*(V21/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f>+(AA21/365)*Y21</f>
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <f>+AB21*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <f>+AB21+AC21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="W22">
+        <f>+T22*S22</f>
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <f>U22-W22</f>
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <f>+F22-E22</f>
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <f>+X22*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <f>+(X22*(V22/1000)+(Z22*(V22/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <f>+(AA22/365)*Y22</f>
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <f>+AB22*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <f>+AB22+AC22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="W23">
+        <f>+T23*S23</f>
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <f>U23-W23</f>
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <f>+F23-E23</f>
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <f>+X23*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <f>+(X23*(V23/1000)+(Z23*(V23/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f>+(AA23/365)*Y23</f>
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <f>+AB23*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <f>+AB23+AC23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="W24">
+        <f>+T24*S24</f>
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <f>U24-W24</f>
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <f>+F24-E24</f>
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <f>+X24*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <f>+(X24*(V24/1000)+(Z24*(V24/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <f>+(AA24/365)*Y24</f>
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <f>+AB24*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <f>+AB24+AC24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="W25">
+        <f>+T25*S25</f>
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <f>U25-W25</f>
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <f>+F25-E25</f>
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <f>+X25*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <f>+(X25*(V25/1000)+(Z25*(V25/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <f>+(AA25/365)*Y25</f>
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <f>+AB25*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <f>+AB25+AC25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="W26">
+        <f>+T26*S26</f>
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <f>U26-W26</f>
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <f>+F26-E26</f>
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <f>+X26*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <f>+(X26*(V26/1000)+(Z26*(V26/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <f>+(AA26/365)*Y26</f>
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <f>+AB26*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <f>+AB26+AC26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="W27">
+        <f>+T27*S27</f>
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <f>U27-W27</f>
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <f>+F27-E27</f>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f>+X27*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <f>+(X27*(V27/1000)+(Z27*(V27/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f>+(AA27/365)*Y27</f>
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <f>+AB27*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <f>+AB27+AC27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="W28">
+        <f>+T28*S28</f>
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <f>U28-W28</f>
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <f>+F28-E28</f>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f>+X28*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <f>+(X28*(V28/1000)+(Z28*(V28/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <f>+(AA28/365)*Y28</f>
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <f>+AB28*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <f>+AB28+AC28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="W29">
+        <f>+T29*S29</f>
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <f>U29-W29</f>
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <f>+F29-E29</f>
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <f>+X29*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <f>+(X29*(V29/1000)+(Z29*(V29/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <f>+(AA29/365)*Y29</f>
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <f>+AB29*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <f>+AB29+AC29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="W30">
+        <f>+T30*S30</f>
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <f>U30-W30</f>
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <f>+F30-E30</f>
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <f>+X30*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <f>+(X30*(V30/1000)+(Z30*(V30/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <f>+(AA30/365)*Y30</f>
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <f>+AB30*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <f>+AB30+AC30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="W31">
+        <f>+T31*S31</f>
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <f>U31-W31</f>
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <f>+F31-E31</f>
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <f>+X31*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <f>+(X31*(V31/1000)+(Z31*(V31/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <f>+(AA31/365)*Y31</f>
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <f>+AB31*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <f>+AB31+AC31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="W32">
+        <f>+T32*S32</f>
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <f>U32-W32</f>
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <f>+F32-E32</f>
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <f>+X32*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <f>+(X32*(V32/1000)+(Z32*(V32/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <f>+(AA32/365)*Y32</f>
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <f>+AB32*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <f>+AB32+AC32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="W33">
+        <f>+T33*S33</f>
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <f>U33-W33</f>
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <f>+F33-E33</f>
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <f>+X33*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <f>+(X33*(V33/1000)+(Z33*(V33/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <f>+(AA33/365)*Y33</f>
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <f>+AB33*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <f>+AB33+AC33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="W34">
+        <f>+T34*S34</f>
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <f>U34-W34</f>
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <f>+F34-E34</f>
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <f>+X34*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <f>+(X34*(V34/1000)+(Z34*(V34/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <f>+(AA34/365)*Y34</f>
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <f>+AB34*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <f>+AB34+AC34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="W35">
+        <f>+T35*S35</f>
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <f>U35-W35</f>
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <f>+F35-E35</f>
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <f>+X35*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <f>+(X35*(V35/1000)+(Z35*(V35/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <f>+(AA35/365)*Y35</f>
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <f>+AB35*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <f>+AB35+AC35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="W36">
+        <f>+T36*S36</f>
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <f>U36-W36</f>
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <f>+F36-E36</f>
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <f>+X36*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <f>+(X36*(V36/1000)+(Z36*(V36/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <f>+(AA36/365)*Y36</f>
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <f>+AB36*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <f>+AB36+AC36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="W37">
+        <f>+T37*S37</f>
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <f>U37-W37</f>
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <f>+F37-E37</f>
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <f>+X37*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <f>+(X37*(V37/1000)+(Z37*(V37/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <f>+(AA37/365)*Y37</f>
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <f>+AB37*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <f>+AB37+AC37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="W38">
+        <f>+T38*S38</f>
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <f>U38-W38</f>
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <f>+F38-E38</f>
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <f>+X38*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <f>+(X38*(V38/1000)+(Z38*(V38/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <f>+(AA38/365)*Y38</f>
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <f>+AB38*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <f>+AB38+AC38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="W39">
+        <f>+T39*S39</f>
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <f>U39-W39</f>
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <f>+F39-E39</f>
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <f>+X39*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <f>+(X39*(V39/1000)+(Z39*(V39/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <f>+(AA39/365)*Y39</f>
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <f>+AB39*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <f>+AB39+AC39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="W40">
+        <f>+T40*S40</f>
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <f>U40-W40</f>
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <f>+F40-E40</f>
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <f>+X40*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <f>+(X40*(V40/1000)+(Z40*(V40/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <f>+(AA40/365)*Y40</f>
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <f>+AB40*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <f>+AB40+AC40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="W41">
+        <f>+T41*S41</f>
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <f>U41-W41</f>
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <f>+F41-E41</f>
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <f>+X41*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <f>+(X41*(V41/1000)+(Z41*(V41/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <f>+(AA41/365)*Y41</f>
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <f>+AB41*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <f>+AB41+AC41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="W42">
+        <f>+T42*S42</f>
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <f>U42-W42</f>
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <f>+F42-E42</f>
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <f>+X42*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <f>+(X42*(V42/1000)+(Z42*(V42/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <f>+(AA42/365)*Y42</f>
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <f>+AB42*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <f>+AB42+AC42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="W43">
+        <f>+T43*S43</f>
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <f>U43-W43</f>
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <f>+F43-E43</f>
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <f>+X43*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <f>+(X43*(V43/1000)+(Z43*(V43/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <f>+(AA43/365)*Y43</f>
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <f>+AB43*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <f>+AB43+AC43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="W44">
+        <f>+T44*S44</f>
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <f>U44-W44</f>
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <f>+F44-E44</f>
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <f>+X44*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <f>+(X44*(V44/1000)+(Z44*(V44/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <f>+(AA44/365)*Y44</f>
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <f>+AB44*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <f>+AB44+AC44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="W45">
+        <f>+T45*S45</f>
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <f>U45-W45</f>
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <f>+F45-E45</f>
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <f>+X45*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <f>+(X45*(V45/1000)+(Z45*(V45/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <f>+(AA45/365)*Y45</f>
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <f>+AB45*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <f>+AB45+AC45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="W46">
+        <f>+T46*S46</f>
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <f>U46-W46</f>
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <f>+F46-E46</f>
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <f>+X46*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <f>+(X46*(V46/1000)+(Z46*(V46/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <f>+(AA46/365)*Y46</f>
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <f>+AB46*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <f>+AB46+AC46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="W47">
+        <f>+T47*S47</f>
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <f>U47-W47</f>
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <f>+F47-E47</f>
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <f>+X47*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <f>+(X47*(V47/1000)+(Z47*(V47/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <f>+(AA47/365)*Y47</f>
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <f>+AB47*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <f>+AB47+AC47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="W48">
+        <f>+T48*S48</f>
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <f>U48-W48</f>
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <f>+F48-E48</f>
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <f>+X48*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <f>+(X48*(V48/1000)+(Z48*(V48/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <f>+(AA48/365)*Y48</f>
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <f>+AB48*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <f>+AB48+AC48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="W49">
+        <f>+T49*S49</f>
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <f>U49-W49</f>
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <f>+F49-E49</f>
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <f>+X49*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <f>+(X49*(V49/1000)+(Z49*(V49/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <f>+(AA49/365)*Y49</f>
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <f>+AB49*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <f>+AB49+AC49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="W50">
+        <f>+T50*S50</f>
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <f>U50-W50</f>
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <f>+F50-E50</f>
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <f>+X50*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <f>+(X50*(V50/1000)+(Z50*(V50/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <f>+(AA50/365)*Y50</f>
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <f>+AB50*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <f>+AB50+AC50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="W51">
+        <f>+T51*S51</f>
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <f>U51-W51</f>
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <f>+F51-E51</f>
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <f>+X51*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <f>+(X51*(V51/1000)+(Z51*(V51/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <f>+(AA51/365)*Y51</f>
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <f>+AB51*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <f>+AB51+AC51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="W52">
+        <f>+T52*S52</f>
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <f>U52-W52</f>
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <f>+F52-E52</f>
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <f>+X52*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <f>+(X52*(V52/1000)+(Z52*(V52/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <f>+(AA52/365)*Y52</f>
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <f>+AB52*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <f>+AB52+AC52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="W53">
+        <f>+T53*S53</f>
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <f>U53-W53</f>
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <f>+F53-E53</f>
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <f>+X53*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <f>+(X53*(V53/1000)+(Z53*(V53/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <f>+(AA53/365)*Y53</f>
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <f>+AB53*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <f>+AB53+AC53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="W54">
+        <f>+T54*S54</f>
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <f>U54-W54</f>
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <f>+F54-E54</f>
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <f>+X54*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <f>+(X54*(V54/1000)+(Z54*(V54/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <f>+(AA54/365)*Y54</f>
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <f>+AB54*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <f>+AB54+AC54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="W55">
+        <f>+T55*S55</f>
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <f>U55-W55</f>
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <f>+F55-E55</f>
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <f>+X55*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <f>+(X55*(V55/1000)+(Z55*(V55/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <f>+(AA55/365)*Y55</f>
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <f>+AB55*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <f>+AB55+AC55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="W56">
+        <f>+T56*S56</f>
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <f>U56-W56</f>
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <f>+F56-E56</f>
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <f>+X56*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <f>+(X56*(V56/1000)+(Z56*(V56/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <f>+(AA56/365)*Y56</f>
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <f>+AB56*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <f>+AB56+AC56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="W57">
+        <f>+T57*S57</f>
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <f>U57-W57</f>
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <f>+F57-E57</f>
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <f>+X57*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <f>+(X57*(V57/1000)+(Z57*(V57/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <f>+(AA57/365)*Y57</f>
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <f>+AB57*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <f>+AB57+AC57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="W58">
+        <f>+T58*S58</f>
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <f>U58-W58</f>
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <f>+F58-E58</f>
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <f>+X58*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <f>+(X58*(V58/1000)+(Z58*(V58/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <f>+(AA58/365)*Y58</f>
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <f>+AB58*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <f>+AB58+AC58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="W59">
+        <f>+T59*S59</f>
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <f>U59-W59</f>
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <f>+F59-E59</f>
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <f>+X59*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <f>+(X59*(V59/1000)+(Z59*(V59/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <f>+(AA59/365)*Y59</f>
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <f>+AB59*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <f>+AB59+AC59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="W60">
+        <f>+T60*S60</f>
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <f>U60-W60</f>
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <f>+F60-E60</f>
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <f>+X60*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <f>+(X60*(V60/1000)+(Z60*(V60/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <f>+(AA60/365)*Y60</f>
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <f>+AB60*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <f>+AB60+AC60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="W61">
+        <f>+T61*S61</f>
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <f>U61-W61</f>
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <f>+F61-E61</f>
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <f>+X61*$AF$1</f>
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <f>+(X61*(V61/1000)+(Z61*(V61/2/1000)))</f>
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <f>+(AA61/365)*Y61</f>
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <f>+AB61*0.19</f>
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <f>+AB61+AC61</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AP54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AP61"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/lib/plantillas-aseguradoras/previsora.xlsx
+++ b/lib/plantillas-aseguradoras/previsora.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Hoja3" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FORMATO '!$A$1:$AF$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FORMATO '!$A$1:$AG$1</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -52,7 +52,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="8">
+  <numFmts count="13">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -60,7 +62,10 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;\ * #,##0.00_);_(&quot;$&quot;\ * \(#,##0.00\);_(&quot;$&quot;\ * &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;\ * #,##0_);_(&quot;$&quot;\ * \(#,##0\);_(&quot;$&quot;\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="&quot; &quot;&quot;$&quot;#,##0.00&quot; &quot;;&quot;-&quot;&quot;$&quot;#,##0.00&quot; &quot;;&quot; &quot;&quot;$&quot;&quot;-&quot;00&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -443,7 +448,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Agencia</v>
+        <v>Intermediario</v>
       </c>
       <c r="B1" t="str">
         <v>Tipo de endoso (Comercial / Reconstrucción)</v>
